--- a/AAII_Financials/Quarterly/AEL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AEL_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="92">
   <si>
     <t>AEL</t>
   </si>
@@ -656,416 +656,428 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>813100</v>
+      </c>
+      <c r="E8" s="3">
         <v>562800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>995800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>478900</v>
       </c>
-      <c r="G8" s="3">
-        <v>654500</v>
-      </c>
       <c r="H8" s="3">
+        <v>618800</v>
+      </c>
+      <c r="I8" s="3">
         <v>414300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>420900</v>
       </c>
-      <c r="J8" s="3" t="s">
+      <c r="K8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1109300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>542600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1075400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>962200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1029700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>798700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>919900</v>
       </c>
-      <c r="R8" s="3" t="s">
+      <c r="S8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1115800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>643400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>706400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1000700</v>
       </c>
-      <c r="W8" s="3" t="s">
+      <c r="X8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1193700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>685500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>118900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1239300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>924300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>819600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>927300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>622800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>630100</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>72400</v>
+      </c>
+      <c r="E9" s="3">
         <v>70600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>68500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>68200</v>
       </c>
-      <c r="G9" s="3">
-        <v>64300</v>
-      </c>
       <c r="H9" s="3">
+        <v>66800</v>
+      </c>
+      <c r="I9" s="3">
         <v>71700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>72500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>73000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>83000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>-1600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>-16900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>203800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>26100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>622600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>-119900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>120700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>133600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>-120900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>29900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>45100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>-8800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>81100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>115000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>140600</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>93700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>23000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>49500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>89700</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>175500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>98100</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>740700</v>
+      </c>
+      <c r="E10" s="3">
         <v>492200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>927300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>410700</v>
       </c>
-      <c r="G10" s="3">
-        <v>590200</v>
-      </c>
       <c r="H10" s="3">
+        <v>552000</v>
+      </c>
+      <c r="I10" s="3">
         <v>342600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>348400</v>
       </c>
-      <c r="J10" s="3" t="s">
+      <c r="K10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1026300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>544200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1092300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>758400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1003600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>176100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1039800</v>
       </c>
-      <c r="R10" s="3" t="s">
+      <c r="S10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>982200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>764300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>676500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>955600</v>
       </c>
-      <c r="W10" s="3" t="s">
+      <c r="X10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1112600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>570500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>-21700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1145600</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>901300</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>770100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>837600</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>447300</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>532000</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1098,8 +1110,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1190,8 +1203,11 @@
       <c r="AF12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1282,8 +1298,11 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1311,12 +1330,12 @@
       <c r="K14" s="3">
         <v>0</v>
       </c>
-      <c r="L14" s="3" t="s">
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
@@ -1330,13 +1349,13 @@
         <v>0</v>
       </c>
       <c r="R14" s="3">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="S14" s="3">
         <v>2000</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>8</v>
+      <c r="T14" s="3">
+        <v>2000</v>
       </c>
       <c r="U14" s="3" t="s">
         <v>8</v>
@@ -1344,8 +1363,8 @@
       <c r="V14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
+      <c r="W14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X14" s="3">
         <v>0</v>
@@ -1353,29 +1372,32 @@
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-      <c r="Z14" s="3" t="s">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
       <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3">
         <v>18400</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>400</v>
       </c>
-      <c r="AD14" s="3" t="s">
+      <c r="AE14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF14" s="3" t="s">
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1466,8 +1488,11 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,192 +1522,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>394600</v>
+      </c>
+      <c r="E17" s="3">
         <v>391400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>318600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>254000</v>
       </c>
-      <c r="G17" s="3">
-        <v>339100</v>
-      </c>
       <c r="H17" s="3">
+        <v>238800</v>
+      </c>
+      <c r="I17" s="3">
         <v>253100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>324400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>477400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>800500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>873500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>864400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>875700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>443200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1671700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>101200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>650200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>677100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>369800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>345200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>263400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>276400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>592000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>662900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>798500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>830400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>596800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>592200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>610600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>575400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>486500</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>418500</v>
+      </c>
+      <c r="E18" s="3">
         <v>171400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>677200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>224900</v>
       </c>
-      <c r="G18" s="3">
-        <v>315400</v>
-      </c>
       <c r="H18" s="3">
+        <v>380000</v>
+      </c>
+      <c r="I18" s="3">
         <v>161200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>96500</v>
       </c>
-      <c r="J18" s="3" t="s">
+      <c r="K18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>308800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-330900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>211000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>86500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>586500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-873000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>818700</v>
       </c>
-      <c r="R18" s="3" t="s">
+      <c r="S18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>438700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>273600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>361200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>737300</v>
       </c>
-      <c r="W18" s="3" t="s">
+      <c r="X18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>601700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>22600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-679600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>408900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>327500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>227400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>316700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>47400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>143600</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1715,224 +1747,231 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-977100</v>
+      </c>
+      <c r="E20" s="3">
         <v>451800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-213800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-404500</v>
       </c>
-      <c r="G20" s="3">
-        <v>-342500</v>
-      </c>
       <c r="H20" s="3">
+        <v>-342400</v>
+      </c>
+      <c r="I20" s="3">
         <v>415300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>886000</v>
       </c>
-      <c r="J20" s="3" t="s">
+      <c r="K20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-186800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>536400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-273700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>282400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-568800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>1732500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1126900</v>
       </c>
-      <c r="R20" s="3" t="s">
+      <c r="S20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-147800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-212300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-327600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-766300</v>
       </c>
-      <c r="W20" s="3" t="s">
+      <c r="X20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-383700</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>101900</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>867200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-290900</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-229700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-175000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-224200</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>151100</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-144400</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-483700</v>
+      </c>
+      <c r="E21" s="3">
         <v>695900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>532700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-108300</v>
       </c>
-      <c r="G21" s="3">
-        <v>38700</v>
-      </c>
       <c r="H21" s="3">
+        <v>-227900</v>
+      </c>
+      <c r="I21" s="3">
         <v>762400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1132800</v>
       </c>
-      <c r="J21" s="3" t="s">
+      <c r="K21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>206500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>205100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-78400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>574300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>45100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1483400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-426700</v>
       </c>
-      <c r="R21" s="3" t="s">
+      <c r="S21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>425600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-58600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>64500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>17100</v>
       </c>
-      <c r="W21" s="3" t="s">
+      <c r="X21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>299900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>240300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>329200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>212800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>121700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>102900</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>183200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>374900</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>98500</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E22" s="3">
         <v>13300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>12600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>12400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>11600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>10300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>7800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>7700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>7600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>7900</v>
-      </c>
-      <c r="M22" s="3">
-        <v>7700</v>
       </c>
       <c r="N22" s="3">
         <v>7700</v>
@@ -1947,236 +1986,245 @@
         <v>7700</v>
       </c>
       <c r="R22" s="3">
+        <v>7700</v>
+      </c>
+      <c r="S22" s="3">
         <v>8000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>10000</v>
-      </c>
-      <c r="T22" s="3">
-        <v>10400</v>
       </c>
       <c r="U22" s="3">
         <v>10400</v>
       </c>
       <c r="V22" s="3">
+        <v>10400</v>
+      </c>
+      <c r="W22" s="3">
         <v>10500</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>10400</v>
-      </c>
-      <c r="X22" s="3">
-        <v>10300</v>
       </c>
       <c r="Y22" s="3">
         <v>10300</v>
       </c>
       <c r="Z22" s="3">
+        <v>10300</v>
+      </c>
+      <c r="AA22" s="3">
         <v>10000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>10200</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>11100</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>12100</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>11100</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>10900</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>10100</v>
       </c>
     </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-571700</v>
+      </c>
+      <c r="E23" s="3">
         <v>609800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>450800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-191900</v>
       </c>
-      <c r="G23" s="3">
-        <v>-38600</v>
-      </c>
       <c r="H23" s="3">
+        <v>26100</v>
+      </c>
+      <c r="I23" s="3">
         <v>566300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>974700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>864700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>114400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>197600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-70400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>361200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>9900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>851800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-315900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>270200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>280800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>51000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>23200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-39500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>66200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>207700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>114200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>177600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>107700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>86800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>40300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>81500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>187600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-11000</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-108200</v>
+      </c>
+      <c r="E24" s="3">
         <v>133700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>95700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-36000</v>
       </c>
-      <c r="G24" s="3">
-        <v>-20500</v>
-      </c>
       <c r="H24" s="3">
+        <v>-6800</v>
+      </c>
+      <c r="I24" s="3">
         <v>121400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>211400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>185200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>21300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>44700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-15700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>78500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>184600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-68500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>27200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>60700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>13600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>4600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-9500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>12400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>38300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>20300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>36600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>35000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>29800</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>13300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>27500</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>66800</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-3600</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,192 +2315,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-463500</v>
+      </c>
+      <c r="E26" s="3">
         <v>476100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>355100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-155900</v>
       </c>
-      <c r="G26" s="3">
-        <v>-18100</v>
-      </c>
       <c r="H26" s="3">
+        <v>32900</v>
+      </c>
+      <c r="I26" s="3">
         <v>444900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>763300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>679500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>93100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>152900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-54700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>282700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>8700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>667200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-247400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>242900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>220200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>37400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>18600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-30000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>53800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>169300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>93900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>141000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>72700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>57000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>26900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>53900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>120800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-7400</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-475900</v>
+      </c>
+      <c r="E27" s="3">
         <v>465200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>344400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-166900</v>
       </c>
-      <c r="G27" s="3">
-        <v>-29400</v>
-      </c>
       <c r="H27" s="3">
+        <v>21700</v>
+      </c>
+      <c r="I27" s="3">
         <v>434000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>752400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>668500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>82200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>141900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-65600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>271800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-6300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>661300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-253400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>236300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>220200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>37400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>18600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-30000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>53800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>169300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>93900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>141000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>72700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>57000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>26900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>53900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>120800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-7400</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,8 +2600,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2599,17 +2659,17 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>8</v>
+      <c r="U29" s="3">
+        <v>0</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W29" s="3">
-        <v>0</v>
-      </c>
-      <c r="X29" s="3" t="s">
+      <c r="W29" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="X29" s="3">
+        <v>0</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>8</v>
@@ -2617,11 +2677,11 @@
       <c r="Z29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AA29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB29" s="3">
         <v>-35900</v>
-      </c>
-      <c r="AB29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>8</v>
@@ -2635,8 +2695,11 @@
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2790,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,192 +2885,201 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>977100</v>
+      </c>
+      <c r="E32" s="3">
         <v>-451800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>213800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>404500</v>
       </c>
-      <c r="G32" s="3">
-        <v>342500</v>
-      </c>
       <c r="H32" s="3">
+        <v>342400</v>
+      </c>
+      <c r="I32" s="3">
         <v>-415300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-886000</v>
       </c>
-      <c r="J32" s="3" t="s">
+      <c r="K32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>186800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-536400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>273700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-282400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>568800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-1732500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1126900</v>
       </c>
-      <c r="R32" s="3" t="s">
+      <c r="S32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>147800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>212300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>327600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>766300</v>
       </c>
-      <c r="W32" s="3" t="s">
+      <c r="X32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>383700</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-101900</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-867200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>290900</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>229700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>175000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>224200</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-151100</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>144400</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-475900</v>
+      </c>
+      <c r="E33" s="3">
         <v>465200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>344400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-166900</v>
       </c>
-      <c r="G33" s="3">
-        <v>-29400</v>
-      </c>
       <c r="H33" s="3">
+        <v>21700</v>
+      </c>
+      <c r="I33" s="3">
         <v>434000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>752400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>668500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>82200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>141900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-65600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>271800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-6300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>661300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-253400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>236300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>220200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>37400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>18600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-30000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>53800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>169300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>93900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>141000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>36800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>57000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>26900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>53900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>120800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-7400</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,197 +3170,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-475900</v>
+      </c>
+      <c r="E35" s="3">
         <v>465200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>344400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-166900</v>
       </c>
-      <c r="G35" s="3">
-        <v>-29400</v>
-      </c>
       <c r="H35" s="3">
+        <v>21700</v>
+      </c>
+      <c r="I35" s="3">
         <v>434000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>752400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>668500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>82200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>141900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-65600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>271800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-6300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>661300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-253400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>236300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>220200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>37400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>18600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-30000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>53800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>169300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>93900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>141000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>36800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>57000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>26900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>53900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>120800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-7400</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3402,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,100 +3437,104 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>9772600</v>
+      </c>
+      <c r="E41" s="3">
         <v>10188400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>5000700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2777900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1919700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1808100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1287200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1933900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>4509000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>12684800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>11524300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>11087100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>9095500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2656600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2408600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1833100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>2293400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1138700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1216000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1115900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>344400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1129200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1259700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>723800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1434000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1285700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1574900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1172700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>791300</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>812800</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3536,8 +3625,11 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3628,8 +3720,11 @@
       <c r="AF43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3720,8 +3815,11 @@
       <c r="AF44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3812,8 +3910,11 @@
       <c r="AF45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3904,100 +4005,106 @@
       <c r="AF46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>43853300</v>
+        <v>47499400</v>
       </c>
       <c r="E47" s="3">
-        <v>50387200</v>
+        <v>44199800</v>
       </c>
       <c r="F47" s="3">
-        <v>50734300</v>
+        <v>50621600</v>
       </c>
       <c r="G47" s="3">
-        <v>50893600</v>
+        <v>50964600</v>
       </c>
       <c r="H47" s="3">
+        <v>51123400</v>
+      </c>
+      <c r="I47" s="3">
         <v>51223200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>54337000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>57906300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>59099000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>51307300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>52179700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>50889400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>52294500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>56123200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>55176100</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>51871100</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>55521600</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>55760900</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>53897200</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>51448900</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>49222300</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>49328000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>48179800</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>48809900</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>48732300</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>47618000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>46838500</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>44998700</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>43927000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>45105300</v>
       </c>
     </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4088,8 +4195,11 @@
       <c r="AF48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4180,8 +4290,11 @@
       <c r="AF49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4385,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,31 +4480,34 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>152700</v>
+      </c>
+      <c r="E52" s="3">
         <v>425400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>293500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>290600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>438400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>246500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>76900</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>8</v>
@@ -4405,59 +4524,62 @@
       <c r="O52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P52" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q52" s="3" t="s">
+      <c r="P52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R52" s="3">
+      <c r="Q52" s="3">
+        <v>0</v>
+      </c>
+      <c r="R52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S52" s="3">
         <v>90400</v>
       </c>
-      <c r="S52" s="3">
-        <v>0</v>
-      </c>
       <c r="T52" s="3">
         <v>0</v>
       </c>
       <c r="U52" s="3">
+        <v>0</v>
+      </c>
+      <c r="V52" s="3">
         <v>9300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>152000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>291200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>250700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>221600</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>159600</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>38100</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>35500</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>64100</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>126700</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>168600</v>
       </c>
-      <c r="AF52" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,100 +4670,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>79918300</v>
+      </c>
+      <c r="E54" s="3">
         <v>76712900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>77645400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>74495700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>73183600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>70185000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>71663300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>74899300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>78349100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>78318000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>73882300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>72677700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>71688600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>68665100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>68608300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>65549600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>69696600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>68330000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>66371300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>64482200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>61625600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>63449000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>61627500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>61301300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>62030700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>60379700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>59635600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>57548600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>56053500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>55848200</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4802,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,8 +4837,9 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4800,8 +4930,11 @@
       <c r="AF57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4892,100 +5025,106 @@
       <c r="AF58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>69686900</v>
+      </c>
+      <c r="E59" s="3">
         <v>68562100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>67624200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>66310000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>65872100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>64639300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>65739700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>67159400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>68829400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>65079200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>64789600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>63773600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>62593800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>60351800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>61913400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>61053300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>62150500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>61657000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>60466700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>59505800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>57986200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>58380300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>57136300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>56561600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>56459800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>55243400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>54252600</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>53014200</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>51935400</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>51117500</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5076,100 +5215,106 @@
       <c r="AF60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>864600</v>
+      </c>
+      <c r="E61" s="3">
         <v>866100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>867700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>869300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>870800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>873500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>575100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>574900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>574700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>574400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>574200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>574000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>573800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>573600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>573400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>573100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>652400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>738300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>738100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>737800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>737600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>737300</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>737100</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>736900</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>736700</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>736100</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1130700</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>736000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>735600</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>735200</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5182,8 +5327,8 @@
       <c r="F62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G62" s="3">
-        <v>0</v>
+      <c r="G62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H62" s="3">
         <v>0</v>
@@ -5192,40 +5337,40 @@
         <v>0</v>
       </c>
       <c r="J62" s="3">
+        <v>0</v>
+      </c>
+      <c r="K62" s="3">
         <v>219000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>542000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>426200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>483600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>376900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>504000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>512400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>229800</v>
       </c>
-      <c r="R62" s="3">
-        <v>0</v>
-      </c>
       <c r="S62" s="3">
+        <v>0</v>
+      </c>
+      <c r="T62" s="3">
         <v>177900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>143200</v>
-      </c>
-      <c r="U62" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="V62" s="3" t="s">
         <v>8</v>
@@ -5242,8 +5387,8 @@
       <c r="Z62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA62" s="3">
-        <v>0</v>
+      <c r="AA62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB62" s="3">
         <v>0</v>
@@ -5251,17 +5396,20 @@
       <c r="AC62" s="3">
         <v>0</v>
       </c>
-      <c r="AD62" s="3" t="s">
-        <v>8</v>
+      <c r="AD62" s="3">
+        <v>0</v>
       </c>
       <c r="AE62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AF62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG62" s="3">
         <v>110600</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5500,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5595,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,100 +5690,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>76895000</v>
+      </c>
+      <c r="E66" s="3">
         <v>74659300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>75073500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>71890200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>70834100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>66977300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>67781000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>69728300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>72026000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>71942800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>67586600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>66748900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>65339600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>62546300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>63546200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>62026800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>65126400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>64203300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>62873800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>61542600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>59226500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>60959700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>59200700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>58754300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>59180600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>57617000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>56984200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>55112400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>53761900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>53035400</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5822,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +5915,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6010,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5938,8 +6105,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,100 +6200,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>4852400</v>
+      </c>
+      <c r="E72" s="3">
         <v>5328400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>4863100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>4518700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>4685600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>3974100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>3672400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>3322700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2767400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>2716700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2574700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2640300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2368600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2403700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>1742400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>1995800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>1768800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>1575900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>1538600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>1520000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>1550000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>1521400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>1352100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>1258200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>1244800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>1231100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>1174200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>1147200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>1093300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>993600</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6390,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6485,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,100 +6580,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3023200</v>
+      </c>
+      <c r="E76" s="3">
         <v>2053500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2571900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2605500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2349500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3207700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3882200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>5171100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>6323100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>6375200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>6295700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>5928700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>6349000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>6118700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>5062000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>3522700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>4570100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>4126700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>3497500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>2939500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>2399100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>2489300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>2426800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>2547000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>2850200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>2762700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>2651400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>2436200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>2291600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>2812900</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,197 +6770,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-475900</v>
+      </c>
+      <c r="E81" s="3">
         <v>465200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>344400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-166900</v>
       </c>
-      <c r="G81" s="3">
-        <v>-29400</v>
-      </c>
       <c r="H81" s="3">
+        <v>21700</v>
+      </c>
+      <c r="I81" s="3">
         <v>434000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>752400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>668500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>82200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>141900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-65600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>271800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-6300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>661300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-253400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>236300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>220200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>37400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>18600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-30000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>53800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>169300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>93900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>141000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>36800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>57000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>26900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>53900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>120800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-7400</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,100 +7002,104 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>75000</v>
+      </c>
+      <c r="E83" s="3">
         <v>72700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>69400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>71300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>65700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>185800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>150400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>227700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>84500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>-400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>-15700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>205300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>27500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>624000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>-118500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>121800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>134800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>-120000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>30900</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>46100</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>-7900</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>81900</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>115900</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>141500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>94900</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>23900</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>50600</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>90600</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>176400</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>99400</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7190,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7285,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7380,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7475,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,100 +7570,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>910200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-217900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2382400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>865000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>919100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>812700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>212400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>99900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>3595900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>13000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>152400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>471900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>949800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>683100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>836800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-1164700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1063100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>417000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>759200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1112000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-543100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>729800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>299600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-443200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>657900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>434600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>333400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>498000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>469800</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>522100</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,100 +7702,104 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-14100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-22500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-9400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-4200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-6700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-25900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-5900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-3000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-5300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-6100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-3700</v>
-      </c>
-      <c r="O91" s="3">
-        <v>-800</v>
       </c>
       <c r="P91" s="3">
         <v>-800</v>
       </c>
       <c r="Q91" s="3">
+        <v>-800</v>
+      </c>
+      <c r="R91" s="3">
         <v>-1500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-10100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1700</v>
-      </c>
-      <c r="U91" s="3">
-        <v>-700</v>
       </c>
       <c r="V91" s="3">
         <v>-700</v>
       </c>
       <c r="W91" s="3">
+        <v>-700</v>
+      </c>
+      <c r="X91" s="3">
         <v>-800</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-700</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-1700</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-1100</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-900</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-1400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-1100</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-2800</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-300</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +7890,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,100 +7985,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1299800</v>
+      </c>
+      <c r="E94" s="3">
         <v>5213100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-223200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>804500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-177900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>358200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-189000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-2446200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-7625800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>950900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>329800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>120700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>4505900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-149100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-78400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>856300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-149500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-954200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1026100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-925100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-459800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1251100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-36100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-661300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-684200</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-553700</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-834100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-519900</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-1010300</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-2085600</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,8 +8117,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7977,8 +8210,11 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8305,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8400,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,100 +8495,106 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-26300</v>
+      </c>
+      <c r="E100" s="3">
         <v>192500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>63600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-811400</v>
       </c>
-      <c r="G100" s="3">
-        <v>-629700</v>
-      </c>
       <c r="H100" s="3">
+        <v>-629300</v>
+      </c>
+      <c r="I100" s="3">
         <v>-650000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-670100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-228800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-4145900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>196500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-45000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1399000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>983300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-286000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-182800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-151900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>241000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>460000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>366900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>584600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>218000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>390800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>272400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>394200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>174900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-169200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>903100</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>403500</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>519000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>829200</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8437,96 +8685,102 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-415900</v>
+      </c>
+      <c r="E102" s="3">
         <v>5187800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>2222800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>858200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>111500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>520900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-646700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-2575100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-8175800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1160500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>437100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1991600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>6438900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>248000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>575500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-460300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>1154700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-77200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>100100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>771500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-784800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-130500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>535900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-710300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>148400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-289300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>402200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>381500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-21500</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-734200</v>
       </c>
     </row>
